--- a/i18n/strings-ko.xlsx
+++ b/i18n/strings-ko.xlsx
@@ -739,7 +739,7 @@
         <v>홈 화면</v>
       </c>
       <c r="B31" t="str">
-        <v>모든 그래픽·사운드는 코드로 생성됩니다 · 외부 저작물 없음</v>
+        <v>즐겁게 게임하고 맛있는 K-푸드 받아가세요!</v>
       </c>
       <c r="C31" t="str">
         <v/>
